--- a/EXCEL/SILENT_Sound_Datatable.xlsx
+++ b/EXCEL/SILENT_Sound_Datatable.xlsx
@@ -3753,7 +3753,7 @@
       <c r="H20" s="8" t="n"/>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="E21" s="8" t="n">
-        <v>13017</v>
+        <v>13087</v>
       </c>
       <c r="F21" s="8" t="n">
         <v>15013</v>
@@ -3785,7 +3785,11 @@
       <c r="G21" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="H21" s="8" t="n"/>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>TV가 6번 방 B 물건 묶음(13087) 안에 합쳐져 대상 변경 (R11)</t>
+        </is>
+      </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
           <t>Y</t>

--- a/EXCEL/SILENT_Sound_Datatable.xlsx
+++ b/EXCEL/SILENT_Sound_Datatable.xlsx
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="140" customWidth="1" style="10" min="1" max="1"/>
@@ -546,7 +546,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>파일 6개, 시트 23개. 시트 하나 = CSV 하나(시트 이름.csv, UTF-8). _README · _COLUMNS 시트는 설명용이라 내보내지 않습니다.</t>
+          <t>파일 6개, 시트 16개. 시트 하나 = CSV 하나(시트 이름.csv, UTF-8). _README · _COLUMNS 시트는 설명용이라 내보내지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SILENT_Object_Datatable.xlsx: LOCK, CONSOLE, CARD, FRAME, ARROW, WIRE, FORMULA, PAPER, TV</t>
+          <t>SILENT_Object_Datatable.xlsx: LOCK, CONSOLE</t>
         </is>
       </c>
     </row>
@@ -643,184 +643,164 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  │    └ CARD · FRAME · ARROW · WIRE · FORMULA · PAPER · TV (앵커의 값, AnchorRef)</t>
+          <t xml:space="preserve">  └ PUZZLE (퍼즐, SolverRoom · ClueRoom, 입력 장치 InputAnchor)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ PUZZLE (퍼즐, SolverRoom · ClueRoom, 입력 장치 InputAnchor)</t>
+          <t xml:space="preserve">       ├ PUZZLE_SLOT (정답 칸, PuzzleID)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">       ├ PUZZLE_SLOT (정답 칸, PuzzleID)</t>
+          <t xml:space="preserve">       └ COLOR_LETTER (풀리면 보여 줄 색 글자, PuzzleID, 표시판 SignAnchor)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └ COLOR_LETTER (풀리면 보여 줄 색 글자, PuzzleID, 표시판 SignAnchor)</t>
+          <t>라이브러리: PREFAB ← COMPONENT (Components), SOUND ← SOUND_LINK (SoundID), GAME_CONFIG → CHARACTER_STAT (16010)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>라이브러리: PREFAB ← COMPONENT (Components), SOUND ← SOUND_LINK (SoundID), GAME_CONFIG → CHARACTER_STAT (16010)</t>
+          <t>전체 시트 목록, 부모, 읽는 순서: Settings 파일의 REGISTRY</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>전체 시트 목록, 부모, 읽는 순서: Settings 파일의 REGISTRY</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>공통 규칙</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>공통 규칙</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>1~4행: 1행 그 시트만의 규칙, 2행 기능, 3행 역할, 4행 의도. 5행 열 이름, 6행부터 데이터. CSV 리더는 앞 4줄을 건너뜀</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1~4행: 1행 그 시트만의 규칙, 2행 기능, 3행 역할, 4행 의도. 5행 열 이름, 6행부터 데이터. CSV 리더는 앞 4줄을 건너뜀</t>
+          <t>1열 ID: 숫자, 시트 구간 안에서 차례로. 지운 번호는 다시 쓰지 않음. Object 파일 시트의 1열 AnchorRef는 새 번호가 아니라 앵커 ID(두 앵커 시트가 2001~ 구간을 함께 써서 번호가 겹치지 않음.)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="27.75" customHeight="1" s="10">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1열 ID: 숫자, 시트 구간 안에서 차례로. 지운 번호는 다시 쓰지 않음. Object 파일 시트의 1열 AnchorRef는 새 번호가 아니라 앵커 ID(두 앵커 시트가 2001~ 구간을 함께 써서 번호가 겹치지 않음. 카드는 여러 장이 한 앵커라 CARD만 자기 ID 3001~)</t>
+          <t>2열 Name: 한국어 설명. 겹쳐도 되고 코드가 읽지 않음. 겹치면 안 되는 문자열은 두 앵커 시트의 AnchorID(Unity 앵커 이름) 하나</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2열 Name: 한국어 설명. 겹쳐도 되고 코드가 읽지 않음. 겹치면 안 되는 문자열은 두 앵커 시트의 AnchorID(Unity 앵커 이름) 하나</t>
+          <t>참조: 다른 시트는 숫자 ID로만 가리킴. 여러 개면 | 로 구분</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>참조: 다른 시트는 숫자 ID로만 가리킴. 여러 개면 | 로 구분</t>
+          <t>코드가 읽는 단어 값(색, 방향, 기호, 유형)은 아래 정해진 영어 단어로 씀</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>코드가 읽는 단어 값(색, 방향, 기호, 유형)은 아래 정해진 영어 단어로 씀</t>
+          <t>Active = N인 행은 읽지 않음. 단위: 거리 m, 시간 ms(밀리초, 1000 = 1초, 정수). 좌표는 DataTable에 없음(앵커 자리는 Unity 방 프리팹에서 정함)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Active = N인 행은 읽지 않음. 단위: 거리 m, 시간 ms(밀리초, 1000 = 1초, 정수). 좌표는 DataTable에 없음(앵커 자리는 Unity 방 프리팹에서 정함)</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>정해진 단어</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>정해진 단어</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Colour: Red, Green, Blue, Gray, Black, Orange, Yellow, SkyBlue, Pink, Purple, Crimson, White, Teal, Navy (글자 색 6개의 코드는 아트 01)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Colour: Red, Green, Blue, Gray, Black, Orange, Yellow, SkyBlue, Pink, Purple, Crimson, White, Teal, Navy (글자 색 6개의 코드는 아트 01)</t>
+          <t>Symbol: BlackDiamond ◆, WhiteDiamond ◇, BlackSpade ♠, WhiteSpade ♤, BlackHeart ♥, WhiteHeart ♡, Star ★, Heart (빨간 하트 그림), Spade (검은 스페이드 그림), None</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Symbol: BlackDiamond ◆, WhiteDiamond ◇, BlackSpade ♠, WhiteSpade ♤, BlackHeart ♥, WhiteHeart ♡, Star ★, Heart (빨간 하트 그림), Spade (검은 스페이드 그림), None</t>
+          <t>Direction: Up, Down, Left, Right / Wall: North, South</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Direction: Up, Down, Left, Right / Wall: North, South</t>
+          <t>Role: Solver, Clue / ExitRule: SolvedEach, BothSolved</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Role: Solver, Clue / ExitRule: SolvedEach, BothSolved</t>
+          <t>Type (PUZZLE): CardLetter, FrameCount, ArrowSequence, WireRank, TwistedFormula, TVLetter, ColourWord</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Type (PUZZLE): CardLetter, FrameCount, ArrowSequence, WireRank, TwistedFormula, TVLetter, ColourWord</t>
+          <t>DialFace (LOCK): Number1_9, Number0_9, Letter9, Color6 / DisplayFace: Letter, Color, Number, LetterWindow</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>DecoyType (CARD): None, LetterLetter, NumberNumber, SymbolZero, SymbolOne, SymbolTwo, SymbolThree, SymbolFour, IconIcon</t>
+          <t>Trigger (SOUND_LINK): OnStep, OnInteract, OnCloseUpOpen, OnCloseUpClose, OnDialTurn, OnConfirm, OnButton, OnClear, OnSpawn, OnDoorOpen, OnDoorLocked, OnSolved, OnLetterShow, OnWrong, OnInputUnlock, OnRoomEnter, OnRadioRxStart, OnRadioRxEnd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Category (FORMULA): Definition, Basic, Linear, Quadratic, Cubic, School, Discrete</t>
+          <t>Category (SOUND): Footstep, Interact, ObjectLoop, Door, PuzzleSolved, PuzzleWrong, Ambient, Radio / Space: 2D, 3D / Bus: SFX, Ambient, UI, Radio</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>DialFace (LOCK): Number1_9, Number0_9, Letter9, Color6 / DisplayFace: Letter, Color, Number, LetterWindow</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="27.75" customHeight="1" s="10">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Trigger (SOUND_LINK): OnStep, OnInteract, OnCloseUpOpen, OnCloseUpClose, OnDialTurn, OnConfirm, OnButton, OnClear, OnSpawn, OnDoorOpen, OnDoorLocked, OnSolved, OnLetterShow, OnWrong, OnInputUnlock, OnRoomEnter, OnRadioRxStart, OnRadioRxEnd</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Category (SOUND): Footstep, Interact, ObjectLoop, Door, PuzzleSolved, PuzzleWrong, Ambient, Radio / Space: 2D, 3D / Bus: SFX, Ambient, UI, Radio</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Y / N: Active, IsAnswer (정답에 쓰이는 것 = Y: CARD, FRAME, ARROW, WIRE, FORMULA, PAPER, TV), Flip, Loop, Required</t>
-        </is>
-      </c>
-    </row>
+          <t>Y / N: Active, Flip, Loop, Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="27.75" customHeight="1" s="10"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
